--- a/jogos_2025-07-11.xlsx
+++ b/jogos_2025-07-11.xlsx
@@ -250,45 +250,45 @@
     <t>Aldosivi</t>
   </si>
   <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Toronto II</t>
+  </si>
+  <si>
     <t>Talleres Córdoba</t>
   </si>
   <si>
-    <t>Toronto II</t>
-  </si>
-  <si>
     <t>North Carolina FC</t>
   </si>
   <si>
     <t>Austin II</t>
   </si>
   <si>
+    <t>Gimnasia y Tiro</t>
+  </si>
+  <si>
     <t>Monterey Bay</t>
   </si>
   <si>
-    <t>Gimnasia y Tiro</t>
-  </si>
-  <si>
     <t>Blacktown City</t>
   </si>
   <si>
@@ -298,43 +298,43 @@
     <t>Central Córdoba SdE</t>
   </si>
   <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
     <t>Finn Harps</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
+    <t>New York RB II</t>
+  </si>
+  <si>
     <t>San Lorenzo</t>
   </si>
   <si>
-    <t>New York RB II</t>
-  </si>
-  <si>
     <t>Birmingham Legion</t>
   </si>
   <si>
     <t>St. Louis City II</t>
   </si>
   <si>
+    <t>Patronato</t>
+  </si>
+  <si>
     <t>Orange County SC</t>
-  </si>
-  <si>
-    <t>Patronato</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -912,52 +912,52 @@
         <v>107</v>
       </c>
       <c r="L2">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="M2">
         <v>3.5</v>
       </c>
       <c r="N2">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="O2">
         <v>2.1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q2">
         <v>1.73</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB2">
         <v>1.59</v>
@@ -966,22 +966,22 @@
         <v>2.2</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ2" t="s">
         <v>108</v>
@@ -990,13 +990,13 @@
         <v>108</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO2">
         <v>-1</v>
@@ -1103,13 +1103,13 @@
         <v>1.27</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="V3">
         <v>4.3</v>
@@ -1127,13 +1127,13 @@
         <v>1.14</v>
       </c>
       <c r="AA3">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AB3">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC3">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AD3">
         <v>2.2</v>
@@ -1142,16 +1142,16 @@
         <v>1.53</v>
       </c>
       <c r="AF3">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AG3">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AH3">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="AI3">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AJ3" t="s">
         <v>108</v>
@@ -1160,13 +1160,13 @@
         <v>108</v>
       </c>
       <c r="AL3">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AM3">
         <v>1.23</v>
       </c>
       <c r="AN3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AO3">
         <v>-1</v>
@@ -1422,76 +1422,76 @@
         <v>107</v>
       </c>
       <c r="L5">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="M5">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="N5">
+        <v>3.47</v>
+      </c>
+      <c r="O5">
+        <v>1.73</v>
+      </c>
+      <c r="P5">
+        <v>10</v>
+      </c>
+      <c r="Q5">
+        <v>2.3</v>
+      </c>
+      <c r="R5">
+        <v>1.25</v>
+      </c>
+      <c r="S5">
+        <v>3.6</v>
+      </c>
+      <c r="T5">
+        <v>2.3</v>
+      </c>
+      <c r="U5">
+        <v>1.57</v>
+      </c>
+      <c r="V5">
+        <v>5</v>
+      </c>
+      <c r="W5">
+        <v>1.14</v>
+      </c>
+      <c r="X5">
+        <v>1.02</v>
+      </c>
+      <c r="Y5">
+        <v>13.3</v>
+      </c>
+      <c r="Z5">
+        <v>1.17</v>
+      </c>
+      <c r="AA5">
+        <v>4.8</v>
+      </c>
+      <c r="AB5">
+        <v>1.54</v>
+      </c>
+      <c r="AC5">
+        <v>2.33</v>
+      </c>
+      <c r="AD5">
+        <v>2.25</v>
+      </c>
+      <c r="AE5">
+        <v>1.53</v>
+      </c>
+      <c r="AF5">
+        <v>1.48</v>
+      </c>
+      <c r="AG5">
+        <v>2.57</v>
+      </c>
+      <c r="AH5">
         <v>4.1</v>
       </c>
-      <c r="O5">
-        <v>1.6</v>
-      </c>
-      <c r="P5">
-        <v>8.5</v>
-      </c>
-      <c r="Q5">
-        <v>2.8</v>
-      </c>
-      <c r="R5">
-        <v>1.33</v>
-      </c>
-      <c r="S5">
-        <v>2.9</v>
-      </c>
-      <c r="T5">
-        <v>2.89</v>
-      </c>
-      <c r="U5">
-        <v>1.37</v>
-      </c>
-      <c r="V5">
-        <v>6</v>
-      </c>
-      <c r="W5">
-        <v>1.08</v>
-      </c>
-      <c r="X5">
-        <v>1.03</v>
-      </c>
-      <c r="Y5">
-        <v>9</v>
-      </c>
-      <c r="Z5">
-        <v>1.31</v>
-      </c>
-      <c r="AA5">
-        <v>3.3</v>
-      </c>
-      <c r="AB5">
-        <v>1.78</v>
-      </c>
-      <c r="AC5">
-        <v>1.92</v>
-      </c>
-      <c r="AD5">
-        <v>3.28</v>
-      </c>
-      <c r="AE5">
-        <v>1.3</v>
-      </c>
-      <c r="AF5">
-        <v>1.75</v>
-      </c>
-      <c r="AG5">
-        <v>1.95</v>
-      </c>
-      <c r="AH5">
-        <v>6.45</v>
-      </c>
       <c r="AI5">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="s">
         <v>108</v>
@@ -1500,13 +1500,13 @@
         <v>108</v>
       </c>
       <c r="AL5">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AM5">
         <v>1.22</v>
       </c>
       <c r="AN5">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1548,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="BC5">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="BD5" s="3">
         <v>45849.65625</v>
@@ -1565,7 +1565,7 @@
         <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
         <v>74</v>
@@ -1592,76 +1592,76 @@
         <v>107</v>
       </c>
       <c r="L6">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="N6">
-        <v>4.6</v>
+        <v>2.04</v>
       </c>
       <c r="O6">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="P6">
         <v>9.5</v>
       </c>
       <c r="Q6">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="R6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="T6">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U6">
         <v>1.44</v>
       </c>
       <c r="V6">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AA6">
-        <v>3.62</v>
+        <v>3.42</v>
       </c>
       <c r="AB6">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AD6">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="AE6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF6">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH6">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AI6">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AJ6" t="s">
         <v>108</v>
@@ -1670,46 +1670,46 @@
         <v>108</v>
       </c>
       <c r="AL6">
+        <v>1.67</v>
+      </c>
+      <c r="AM6">
         <v>1.25</v>
       </c>
-      <c r="AM6">
-        <v>1.2</v>
-      </c>
       <c r="AN6">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="AO6">
         <v>-1</v>
       </c>
       <c r="AP6">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ6">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AR6">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AS6">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AT6">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AU6">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV6">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AW6">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AX6">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AY6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ6">
         <v>0</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="BC6">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="BD6" s="3">
         <v>45849.65625</v>
@@ -1762,76 +1762,76 @@
         <v>107</v>
       </c>
       <c r="L7">
+        <v>3.63</v>
+      </c>
+      <c r="M7">
+        <v>3.45</v>
+      </c>
+      <c r="N7">
+        <v>1.81</v>
+      </c>
+      <c r="O7">
+        <v>2.5</v>
+      </c>
+      <c r="P7">
+        <v>9</v>
+      </c>
+      <c r="Q7">
+        <v>1.67</v>
+      </c>
+      <c r="R7">
+        <v>1.3</v>
+      </c>
+      <c r="S7">
+        <v>3.1</v>
+      </c>
+      <c r="T7">
+        <v>2.62</v>
+      </c>
+      <c r="U7">
+        <v>1.47</v>
+      </c>
+      <c r="V7">
+        <v>6</v>
+      </c>
+      <c r="W7">
+        <v>1.1</v>
+      </c>
+      <c r="X7">
+        <v>1.01</v>
+      </c>
+      <c r="Y7">
+        <v>9.5</v>
+      </c>
+      <c r="Z7">
+        <v>1.25</v>
+      </c>
+      <c r="AA7">
+        <v>3.74</v>
+      </c>
+      <c r="AB7">
         <v>1.79</v>
       </c>
-      <c r="M7">
-        <v>3.68</v>
-      </c>
-      <c r="N7">
-        <v>3.47</v>
-      </c>
-      <c r="O7">
-        <v>1.73</v>
-      </c>
-      <c r="P7">
-        <v>10</v>
-      </c>
-      <c r="Q7">
-        <v>2.3</v>
-      </c>
-      <c r="R7">
-        <v>1.25</v>
-      </c>
-      <c r="S7">
-        <v>3.4</v>
-      </c>
-      <c r="T7">
-        <v>2.3</v>
-      </c>
-      <c r="U7">
-        <v>1.57</v>
-      </c>
-      <c r="V7">
-        <v>5</v>
-      </c>
-      <c r="W7">
-        <v>1.14</v>
-      </c>
-      <c r="X7">
-        <v>1.03</v>
-      </c>
-      <c r="Y7">
-        <v>13.3</v>
-      </c>
-      <c r="Z7">
-        <v>1.17</v>
-      </c>
-      <c r="AA7">
-        <v>4.8</v>
-      </c>
-      <c r="AB7">
-        <v>1.54</v>
-      </c>
       <c r="AC7">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="AD7">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="AE7">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AF7">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AH7">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AI7">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
         <v>108</v>
@@ -1840,13 +1840,13 @@
         <v>108</v>
       </c>
       <c r="AL7">
+        <v>1.3</v>
+      </c>
+      <c r="AM7">
+        <v>1.25</v>
+      </c>
+      <c r="AN7">
         <v>1.22</v>
-      </c>
-      <c r="AM7">
-        <v>1.22</v>
-      </c>
-      <c r="AN7">
-        <v>1.8</v>
       </c>
       <c r="AO7">
         <v>-1</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="BC7">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="BD7" s="3">
         <v>45849.65625</v>
@@ -1905,7 +1905,7 @@
         <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
         <v>74</v>
@@ -1932,76 +1932,76 @@
         <v>107</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>1.89</v>
       </c>
       <c r="M8">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N8">
-        <v>2.04</v>
+        <v>3.27</v>
       </c>
       <c r="O8">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="P8">
         <v>9.5</v>
       </c>
       <c r="Q8">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="R8">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
         <v>3.1</v>
       </c>
       <c r="T8">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="U8">
         <v>1.44</v>
       </c>
       <c r="V8">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="W8">
+        <v>1.11</v>
+      </c>
+      <c r="X8">
+        <v>1.05</v>
+      </c>
+      <c r="Y8">
+        <v>9.5</v>
+      </c>
+      <c r="Z8">
+        <v>1.18</v>
+      </c>
+      <c r="AA8">
+        <v>3.98</v>
+      </c>
+      <c r="AB8">
+        <v>1.7</v>
+      </c>
+      <c r="AC8">
+        <v>1.95</v>
+      </c>
+      <c r="AD8">
+        <v>2.89</v>
+      </c>
+      <c r="AE8">
+        <v>1.37</v>
+      </c>
+      <c r="AF8">
+        <v>1.62</v>
+      </c>
+      <c r="AG8">
+        <v>2.1</v>
+      </c>
+      <c r="AH8">
+        <v>5.1</v>
+      </c>
+      <c r="AI8">
         <v>1.1</v>
-      </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>10</v>
-      </c>
-      <c r="Z8">
-        <v>1.29</v>
-      </c>
-      <c r="AA8">
-        <v>3.4</v>
-      </c>
-      <c r="AB8">
-        <v>1.8</v>
-      </c>
-      <c r="AC8">
-        <v>1.9</v>
-      </c>
-      <c r="AD8">
-        <v>3.25</v>
-      </c>
-      <c r="AE8">
-        <v>1.33</v>
-      </c>
-      <c r="AF8">
-        <v>1.68</v>
-      </c>
-      <c r="AG8">
-        <v>2.13</v>
-      </c>
-      <c r="AH8">
-        <v>6.25</v>
-      </c>
-      <c r="AI8">
-        <v>1.11</v>
       </c>
       <c r="AJ8" t="s">
         <v>108</v>
@@ -2010,46 +2010,46 @@
         <v>108</v>
       </c>
       <c r="AL8">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AM8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN8">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AO8">
         <v>-1</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ8">
         <v>0</v>
@@ -2058,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="BC8">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="BD8" s="3">
         <v>45849.65625</v>
@@ -2075,7 +2075,7 @@
         <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
         <v>74</v>
@@ -2102,76 +2102,76 @@
         <v>107</v>
       </c>
       <c r="L9">
-        <v>3.63</v>
+        <v>1.6</v>
       </c>
       <c r="M9">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N9">
-        <v>1.81</v>
+        <v>4.6</v>
       </c>
       <c r="O9">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="P9">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Q9">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="R9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S9">
-        <v>3.21</v>
+        <v>2.98</v>
       </c>
       <c r="T9">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="V9">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
         <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z9">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AA9">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="AB9">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC9">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AD9">
         <v>3.1</v>
       </c>
       <c r="AE9">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH9">
-        <v>5.11</v>
+        <v>5.5</v>
       </c>
       <c r="AI9">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AJ9" t="s">
         <v>108</v>
@@ -2180,46 +2180,46 @@
         <v>108</v>
       </c>
       <c r="AL9">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="AM9">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AN9">
-        <v>1.22</v>
+        <v>2.05</v>
       </c>
       <c r="AO9">
         <v>-1</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ9">
         <v>0</v>
@@ -2228,10 +2228,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="BC9">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="BD9" s="3">
         <v>45849.65625</v>
@@ -2245,7 +2245,7 @@
         <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
         <v>74</v>
@@ -2272,76 +2272,76 @@
         <v>107</v>
       </c>
       <c r="L10">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="M10">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N10">
-        <v>3.27</v>
+        <v>4.1</v>
       </c>
       <c r="O10">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="P10">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="R10">
+        <v>1.39</v>
+      </c>
+      <c r="S10">
+        <v>2.76</v>
+      </c>
+      <c r="T10">
+        <v>2.88</v>
+      </c>
+      <c r="U10">
+        <v>1.36</v>
+      </c>
+      <c r="V10">
+        <v>7</v>
+      </c>
+      <c r="W10">
+        <v>1.09</v>
+      </c>
+      <c r="X10">
+        <v>1.05</v>
+      </c>
+      <c r="Y10">
+        <v>9</v>
+      </c>
+      <c r="Z10">
         <v>1.3</v>
       </c>
-      <c r="S10">
-        <v>3.1</v>
-      </c>
-      <c r="T10">
-        <v>2.45</v>
-      </c>
-      <c r="U10">
-        <v>1.44</v>
-      </c>
-      <c r="V10">
-        <v>6.15</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>9.5</v>
-      </c>
-      <c r="Z10">
-        <v>1.22</v>
-      </c>
       <c r="AA10">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="AB10">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC10">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD10">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="AE10">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AG10">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH10">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AI10">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ10" t="s">
         <v>108</v>
@@ -2350,46 +2350,46 @@
         <v>108</v>
       </c>
       <c r="AL10">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AM10">
         <v>1.22</v>
       </c>
       <c r="AN10">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AO10">
         <v>-1</v>
       </c>
       <c r="AP10">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ10">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR10">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AU10">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV10">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AW10">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX10">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY10">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ10">
         <v>0</v>
@@ -2398,10 +2398,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="BC10">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="BD10" s="3">
         <v>45849.65625</v>
@@ -2460,16 +2460,16 @@
         <v>2.75</v>
       </c>
       <c r="R11">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="S11">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="T11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="U11">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V11">
         <v>12</v>
@@ -2478,16 +2478,16 @@
         <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="Z11">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AB11">
         <v>2.45</v>
@@ -2496,10 +2496,10 @@
         <v>1.48</v>
       </c>
       <c r="AD11">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
         <v>2.2</v>
@@ -2508,10 +2508,10 @@
         <v>1.62</v>
       </c>
       <c r="AH11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI11">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AJ11" t="s">
         <v>108</v>
@@ -2520,13 +2520,13 @@
         <v>108</v>
       </c>
       <c r="AL11">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AM11">
         <v>1.36</v>
       </c>
       <c r="AN11">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AO11">
         <v>-1</v>
@@ -2538,28 +2538,28 @@
         <v>1.38</v>
       </c>
       <c r="AR11">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AS11">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AT11">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="AU11">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="AV11">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AW11">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AX11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AY11">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>74</v>
@@ -2612,40 +2612,40 @@
         <v>107</v>
       </c>
       <c r="L12">
-        <v>2.05</v>
+        <v>2.94</v>
       </c>
       <c r="M12">
-        <v>3.2</v>
+        <v>3.72</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>1.92</v>
       </c>
       <c r="O12">
+        <v>2.2</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
         <v>1.67</v>
       </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>3</v>
-      </c>
       <c r="R12">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
+        <v>3.6</v>
+      </c>
+      <c r="T12">
         <v>2.1</v>
       </c>
-      <c r="T12">
+      <c r="U12">
+        <v>1.65</v>
+      </c>
+      <c r="V12">
         <v>4.5</v>
       </c>
-      <c r="U12">
-        <v>1.18</v>
-      </c>
-      <c r="V12">
-        <v>15</v>
-      </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
         <v>0</v>
@@ -2654,34 +2654,34 @@
         <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.7</v>
+        <v>1.12</v>
       </c>
       <c r="AA12">
-        <v>2.06</v>
+        <v>5.25</v>
       </c>
       <c r="AB12">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC12">
-        <v>1.33</v>
+        <v>2.49</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF12">
-        <v>2.63</v>
+        <v>1.4</v>
       </c>
       <c r="AG12">
-        <v>1.44</v>
+        <v>2.64</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ12" t="s">
         <v>108</v>
@@ -2690,13 +2690,13 @@
         <v>108</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AM12">
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO12">
         <v>-1</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
+        <v>2.2</v>
+      </c>
+      <c r="BC12">
         <v>1.67</v>
-      </c>
-      <c r="BC12">
-        <v>3</v>
       </c>
       <c r="BD12" s="3">
         <v>45849.83333333334</v>
@@ -2755,7 +2755,7 @@
         <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
         <v>74</v>
@@ -2782,40 +2782,40 @@
         <v>107</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>0</v>
@@ -2824,16 +2824,16 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2842,10 +2842,10 @@
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -2908,10 +2908,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD13" s="3">
         <v>45849.83333333334</v>
@@ -2976,13 +2976,13 @@
         <v>2.5</v>
       </c>
       <c r="T14">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U14">
         <v>1.35</v>
       </c>
       <c r="V14">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>1.08</v>
@@ -2994,7 +2994,7 @@
         <v>8.5</v>
       </c>
       <c r="Z14">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA14">
         <v>3.2</v>
@@ -3012,7 +3012,7 @@
         <v>1.27</v>
       </c>
       <c r="AF14">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AG14">
         <v>1.75</v>
@@ -3021,7 +3021,7 @@
         <v>6.5</v>
       </c>
       <c r="AI14">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ14" t="s">
         <v>108</v>
@@ -3036,7 +3036,7 @@
         <v>1.24</v>
       </c>
       <c r="AN14">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AO14">
         <v>-1</v>
@@ -3122,76 +3122,76 @@
         <v>107</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ15" t="s">
         <v>108</v>
@@ -3200,13 +3200,13 @@
         <v>108</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM15">
         <v>0</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO15">
         <v>-1</v>
@@ -3248,10 +3248,10 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BC15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD15" s="3">
         <v>45849.89583333334</v>
@@ -3265,7 +3265,7 @@
         <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>74</v>
@@ -3292,76 +3292,76 @@
         <v>107</v>
       </c>
       <c r="L16">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="M16">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="N16">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="O16">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="P16">
-        <v>8.699999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="Q16">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="R16">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="S16">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="T16">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="U16">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="V16">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="Z16">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AA16">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AC16">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AD16">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="AE16">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH16">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AI16">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AJ16" t="s">
         <v>108</v>
@@ -3370,13 +3370,13 @@
         <v>108</v>
       </c>
       <c r="AL16">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AM16">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AN16">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AO16">
         <v>-1</v>
@@ -3418,10 +3418,10 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BC16">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="BD16" s="3">
         <v>45849.91666666666</v>
@@ -3435,7 +3435,7 @@
         <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
         <v>74</v>
@@ -3462,76 +3462,76 @@
         <v>107</v>
       </c>
       <c r="L17">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="M17">
+        <v>3.15</v>
+      </c>
+      <c r="N17">
         <v>2.95</v>
       </c>
-      <c r="N17">
-        <v>3.35</v>
-      </c>
       <c r="O17">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="P17">
-        <v>5.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q17">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="R17">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="S17">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="U17">
+        <v>1.3</v>
+      </c>
+      <c r="V17">
+        <v>6.8</v>
+      </c>
+      <c r="W17">
+        <v>1.06</v>
+      </c>
+      <c r="X17">
+        <v>1.05</v>
+      </c>
+      <c r="Y17">
+        <v>8</v>
+      </c>
+      <c r="Z17">
+        <v>1.32</v>
+      </c>
+      <c r="AA17">
+        <v>2.95</v>
+      </c>
+      <c r="AB17">
+        <v>2.15</v>
+      </c>
+      <c r="AC17">
+        <v>1.67</v>
+      </c>
+      <c r="AD17">
+        <v>3.8</v>
+      </c>
+      <c r="AE17">
         <v>1.22</v>
       </c>
-      <c r="V17">
-        <v>13</v>
-      </c>
-      <c r="W17">
-        <v>1.04</v>
-      </c>
-      <c r="X17">
-        <v>1.08</v>
-      </c>
-      <c r="Y17">
-        <v>5.55</v>
-      </c>
-      <c r="Z17">
-        <v>1.57</v>
-      </c>
-      <c r="AA17">
-        <v>2.15</v>
-      </c>
-      <c r="AB17">
-        <v>2.88</v>
-      </c>
-      <c r="AC17">
-        <v>1.4</v>
-      </c>
-      <c r="AD17">
-        <v>5.55</v>
-      </c>
-      <c r="AE17">
-        <v>1.08</v>
-      </c>
       <c r="AF17">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AG17">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AH17">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="AI17">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AJ17" t="s">
         <v>108</v>
@@ -3540,13 +3540,13 @@
         <v>108</v>
       </c>
       <c r="AL17">
+        <v>1.35</v>
+      </c>
+      <c r="AM17">
         <v>1.29</v>
       </c>
-      <c r="AM17">
-        <v>1.36</v>
-      </c>
       <c r="AN17">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AO17">
         <v>-1</v>
@@ -3588,10 +3588,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BC17">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="BD17" s="3">
         <v>45849.91666666666</v>

--- a/jogos_2025-07-11.xlsx
+++ b/jogos_2025-07-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="91">
   <si>
     <t>Date</t>
   </si>
@@ -125,60 +125,6 @@
   </si>
   <si>
     <t>awayGoals</t>
-  </si>
-  <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
   </si>
   <si>
     <t>DateTime</t>
@@ -704,10 +650,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD17"/>
+  <dimension ref="A1:AL17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -822,79 +768,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45849</v>
       </c>
       <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>74</v>
-      </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -909,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L2">
         <v>2.7</v>
@@ -984,88 +876,34 @@
         <v>1.17</v>
       </c>
       <c r="AJ2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK2" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL2">
-        <v>1.2</v>
-      </c>
-      <c r="AM2">
-        <v>1.21</v>
-      </c>
-      <c r="AN2">
-        <v>1.25</v>
-      </c>
-      <c r="AO2">
-        <v>-1</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>2.1</v>
-      </c>
-      <c r="BC2">
-        <v>1.73</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45849.27083333334</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45849</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" t="s">
         <v>74</v>
       </c>
-      <c r="E3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" t="s">
-        <v>92</v>
-      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -1079,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L3">
         <v>2.05</v>
@@ -1154,87 +992,33 @@
         <v>1.19</v>
       </c>
       <c r="AJ3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL3">
-        <v>1.37</v>
-      </c>
-      <c r="AM3">
-        <v>1.23</v>
-      </c>
-      <c r="AN3">
-        <v>1.64</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.73</v>
-      </c>
-      <c r="BC3">
-        <v>2.08</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45849.54166666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45849</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1249,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1324,87 +1108,33 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>0</v>
-      </c>
-      <c r="BC4">
-        <v>0</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45849.64583333334</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45849</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1419,7 +1149,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L5">
         <v>1.79</v>
@@ -1494,87 +1224,33 @@
         <v>1.2</v>
       </c>
       <c r="AJ5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL5">
-        <v>1.29</v>
-      </c>
-      <c r="AM5">
-        <v>1.22</v>
-      </c>
-      <c r="AN5">
-        <v>1.8</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.73</v>
-      </c>
-      <c r="BC5">
-        <v>2.3</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45849.65625</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45849</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1589,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -1664,87 +1340,33 @@
         <v>1.09</v>
       </c>
       <c r="AJ6" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL6">
-        <v>1.67</v>
-      </c>
-      <c r="AM6">
-        <v>1.25</v>
-      </c>
-      <c r="AN6">
-        <v>1.33</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>2.3</v>
-      </c>
-      <c r="BC6">
-        <v>1.8</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45849.65625</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45849</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1759,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L7">
         <v>3.63</v>
@@ -1834,87 +1456,33 @@
         <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL7">
-        <v>1.3</v>
-      </c>
-      <c r="AM7">
-        <v>1.25</v>
-      </c>
-      <c r="AN7">
-        <v>1.22</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>2.5</v>
-      </c>
-      <c r="BC7">
-        <v>1.67</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45849.65625</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45849</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1929,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L8">
         <v>1.89</v>
@@ -2004,87 +1572,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ8" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL8">
-        <v>1.29</v>
-      </c>
-      <c r="AM8">
-        <v>1.22</v>
-      </c>
-      <c r="AN8">
-        <v>1.8</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>1.12</v>
-      </c>
-      <c r="AQ8">
-        <v>1.28</v>
-      </c>
-      <c r="AR8">
-        <v>1.53</v>
-      </c>
-      <c r="AS8">
-        <v>1.91</v>
-      </c>
-      <c r="AT8">
-        <v>2.41</v>
-      </c>
-      <c r="AU8">
-        <v>4.57</v>
-      </c>
-      <c r="AV8">
-        <v>3.08</v>
-      </c>
-      <c r="AW8">
-        <v>2.28</v>
-      </c>
-      <c r="AX8">
-        <v>1.79</v>
-      </c>
-      <c r="AY8">
-        <v>1.48</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.73</v>
-      </c>
-      <c r="BC8">
-        <v>2.38</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45849.65625</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45849</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2099,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L9">
         <v>1.6</v>
@@ -2174,87 +1688,33 @@
         <v>1.12</v>
       </c>
       <c r="AJ9" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL9">
-        <v>1.25</v>
-      </c>
-      <c r="AM9">
-        <v>1.2</v>
-      </c>
-      <c r="AN9">
-        <v>2.05</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>1.2</v>
-      </c>
-      <c r="AQ9">
-        <v>1.34</v>
-      </c>
-      <c r="AR9">
-        <v>1.57</v>
-      </c>
-      <c r="AS9">
-        <v>1.88</v>
-      </c>
-      <c r="AT9">
-        <v>2.54</v>
-      </c>
-      <c r="AU9">
-        <v>3.9</v>
-      </c>
-      <c r="AV9">
-        <v>2.9</v>
-      </c>
-      <c r="AW9">
-        <v>2.23</v>
-      </c>
-      <c r="AX9">
-        <v>1.78</v>
-      </c>
-      <c r="AY9">
-        <v>1.43</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.53</v>
-      </c>
-      <c r="BC9">
-        <v>2.9</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45849.65625</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45849</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2269,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L10">
         <v>1.67</v>
@@ -2344,87 +1804,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ10" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL10">
-        <v>1.29</v>
-      </c>
-      <c r="AM10">
-        <v>1.22</v>
-      </c>
-      <c r="AN10">
-        <v>2.05</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.6</v>
-      </c>
-      <c r="BC10">
-        <v>2.8</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45849.65625</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45849</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2439,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L11">
         <v>1.85</v>
@@ -2514,87 +1920,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ11" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL11">
-        <v>1.4</v>
-      </c>
-      <c r="AM11">
-        <v>1.36</v>
-      </c>
-      <c r="AN11">
-        <v>1.6</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>1.17</v>
-      </c>
-      <c r="AQ11">
-        <v>1.38</v>
-      </c>
-      <c r="AR11">
-        <v>1.68</v>
-      </c>
-      <c r="AS11">
-        <v>2.09</v>
-      </c>
-      <c r="AT11">
-        <v>2.71</v>
-      </c>
-      <c r="AU11">
-        <v>3.92</v>
-      </c>
-      <c r="AV11">
-        <v>2.7</v>
-      </c>
-      <c r="AW11">
-        <v>2.05</v>
-      </c>
-      <c r="AX11">
-        <v>1.66</v>
-      </c>
-      <c r="AY11">
-        <v>1.38</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.67</v>
-      </c>
-      <c r="BC11">
-        <v>2.75</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45849.79166666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45849</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2609,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L12">
         <v>2.94</v>
@@ -2684,87 +2036,33 @@
         <v>1.25</v>
       </c>
       <c r="AJ12" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK12" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL12">
-        <v>1.25</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>1.4</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>2.2</v>
-      </c>
-      <c r="BC12">
-        <v>1.67</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45849.83333333334</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45849</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2779,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L13">
         <v>2.05</v>
@@ -2854,87 +2152,33 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.67</v>
-      </c>
-      <c r="BC13">
-        <v>3</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45849.83333333334</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45849</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2949,7 +2193,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L14">
         <v>1.71</v>
@@ -3024,87 +2268,33 @@
         <v>1.07</v>
       </c>
       <c r="AJ14" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL14">
-        <v>1.22</v>
-      </c>
-      <c r="AM14">
-        <v>1.24</v>
-      </c>
-      <c r="AN14">
-        <v>1.95</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>0</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14">
-        <v>0</v>
-      </c>
-      <c r="AV14">
-        <v>0</v>
-      </c>
-      <c r="AW14">
-        <v>0</v>
-      </c>
-      <c r="AX14">
-        <v>0</v>
-      </c>
-      <c r="AY14">
-        <v>0</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.54</v>
-      </c>
-      <c r="BC14">
-        <v>2.85</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45849.85416666666</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45849</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3119,7 +2309,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L15">
         <v>2.62</v>
@@ -3194,102 +2384,48 @@
         <v>1.15</v>
       </c>
       <c r="AJ15" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK15" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL15">
-        <v>1.22</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>1.38</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>2.1</v>
-      </c>
-      <c r="BC15">
-        <v>1.8</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45849.89583333334</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45849</v>
       </c>
       <c r="B16" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
         <v>89</v>
-      </c>
-      <c r="F16" t="s">
-        <v>105</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" t="s">
-        <v>107</v>
       </c>
       <c r="L16">
         <v>2.14</v>
@@ -3364,87 +2500,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ16" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK16" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL16">
-        <v>1.44</v>
-      </c>
-      <c r="AM16">
-        <v>1.36</v>
-      </c>
-      <c r="AN16">
-        <v>1.5</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>0</v>
-      </c>
-      <c r="AQ16">
-        <v>0</v>
-      </c>
-      <c r="AR16">
-        <v>0</v>
-      </c>
-      <c r="AS16">
-        <v>0</v>
-      </c>
-      <c r="AT16">
-        <v>0</v>
-      </c>
-      <c r="AU16">
-        <v>0</v>
-      </c>
-      <c r="AV16">
-        <v>0</v>
-      </c>
-      <c r="AW16">
-        <v>0</v>
-      </c>
-      <c r="AX16">
-        <v>0</v>
-      </c>
-      <c r="AY16">
-        <v>0</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.85</v>
-      </c>
-      <c r="BC16">
-        <v>2.45</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45849.91666666666</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45849</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" t="s">
         <v>72</v>
       </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" t="s">
-        <v>90</v>
-      </c>
       <c r="F17" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3459,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="L17">
         <v>2.25</v>
@@ -3534,66 +2616,12 @@
         <v>1.07</v>
       </c>
       <c r="AJ17" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="AK17" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL17">
-        <v>1.35</v>
-      </c>
-      <c r="AM17">
-        <v>1.29</v>
-      </c>
-      <c r="AN17">
-        <v>1.55</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.86</v>
-      </c>
-      <c r="BC17">
-        <v>2.16</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>90</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45849.91666666666</v>
       </c>
     </row>

--- a/jogos_2025-07-11.xlsx
+++ b/jogos_2025-07-11.xlsx
@@ -196,33 +196,33 @@
     <t>Aldosivi</t>
   </si>
   <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>Wexford</t>
   </si>
   <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
     <t>Vila Nova</t>
   </si>
   <si>
+    <t>Talleres Córdoba</t>
+  </si>
+  <si>
     <t>Toronto II</t>
   </si>
   <si>
-    <t>Talleres Córdoba</t>
-  </si>
-  <si>
     <t>North Carolina FC</t>
   </si>
   <si>
@@ -244,31 +244,31 @@
     <t>Central Córdoba SdE</t>
   </si>
   <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
     <t>Dundalk</t>
   </si>
   <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
     <t>Cork City</t>
   </si>
   <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
     <t>New York RB II</t>
-  </si>
-  <si>
-    <t>San Lorenzo</t>
   </si>
   <si>
     <t>Birmingham Legion</t>
@@ -825,31 +825,31 @@
         <v>1.3</v>
       </c>
       <c r="S2">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T2">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U2">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="V2">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Z2">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AA2">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AB2">
         <v>1.59</v>
@@ -858,22 +858,22 @@
         <v>2.2</v>
       </c>
       <c r="AD2">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AE2">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AF2">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH2">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AI2">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AJ2" t="s">
         <v>90</v>
@@ -938,40 +938,40 @@
         <v>2.08</v>
       </c>
       <c r="R3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S3">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="U3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V3">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="W3">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
         <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="Z3">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA3">
         <v>4.75</v>
       </c>
       <c r="AB3">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AC3">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="AD3">
         <v>2.2</v>
@@ -983,13 +983,13 @@
         <v>1.42</v>
       </c>
       <c r="AG3">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AH3">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AI3">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AJ3" t="s">
         <v>90</v>
@@ -1036,76 +1036,76 @@
         <v>89</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ4" t="s">
         <v>90</v>
@@ -1152,76 +1152,76 @@
         <v>89</v>
       </c>
       <c r="L5">
-        <v>1.79</v>
+        <v>3</v>
       </c>
       <c r="M5">
-        <v>3.68</v>
+        <v>3.38</v>
       </c>
       <c r="N5">
-        <v>3.47</v>
+        <v>2.04</v>
       </c>
       <c r="O5">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P5">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="R5">
+        <v>1.35</v>
+      </c>
+      <c r="S5">
+        <v>2.88</v>
+      </c>
+      <c r="T5">
+        <v>2.72</v>
+      </c>
+      <c r="U5">
+        <v>1.44</v>
+      </c>
+      <c r="V5">
+        <v>6.5</v>
+      </c>
+      <c r="W5">
+        <v>1.11</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>9</v>
+      </c>
+      <c r="Z5">
         <v>1.25</v>
       </c>
-      <c r="S5">
-        <v>3.6</v>
-      </c>
-      <c r="T5">
-        <v>2.3</v>
-      </c>
-      <c r="U5">
-        <v>1.57</v>
-      </c>
-      <c r="V5">
-        <v>5</v>
-      </c>
-      <c r="W5">
-        <v>1.14</v>
-      </c>
-      <c r="X5">
-        <v>1.02</v>
-      </c>
-      <c r="Y5">
-        <v>13.3</v>
-      </c>
-      <c r="Z5">
-        <v>1.17</v>
-      </c>
       <c r="AA5">
-        <v>4.8</v>
+        <v>3.48</v>
       </c>
       <c r="AB5">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AD5">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="AE5">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="AF5">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
-        <v>2.57</v>
+        <v>2.1</v>
       </c>
       <c r="AH5">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AI5">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AJ5" t="s">
         <v>90</v>
@@ -1268,76 +1268,76 @@
         <v>89</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="M6">
-        <v>3.38</v>
+        <v>3.68</v>
       </c>
       <c r="N6">
-        <v>2.04</v>
+        <v>3.47</v>
       </c>
       <c r="O6">
+        <v>1.73</v>
+      </c>
+      <c r="P6">
+        <v>10</v>
+      </c>
+      <c r="Q6">
         <v>2.3</v>
       </c>
-      <c r="P6">
-        <v>9.5</v>
-      </c>
-      <c r="Q6">
-        <v>1.8</v>
-      </c>
       <c r="R6">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="T6">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="U6">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="Z6">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AA6">
-        <v>3.42</v>
+        <v>4.75</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AC6">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AD6">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="AE6">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH6">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="AI6">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AJ6" t="s">
         <v>90</v>
@@ -1408,13 +1408,13 @@
         <v>3.1</v>
       </c>
       <c r="T7">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U7">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W7">
         <v>1.1</v>
@@ -1423,13 +1423,13 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA7">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="AB7">
         <v>1.79</v>
@@ -1438,22 +1438,22 @@
         <v>1.91</v>
       </c>
       <c r="AD7">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AE7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF7">
         <v>1.75</v>
       </c>
       <c r="AG7">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH7">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AI7">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AJ7" t="s">
         <v>90</v>
@@ -1473,7 +1473,7 @@
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1500,40 +1500,40 @@
         <v>89</v>
       </c>
       <c r="L8">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="M8">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="N8">
-        <v>3.27</v>
+        <v>4.1</v>
       </c>
       <c r="O8">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="P8">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q8">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="T8">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U8">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V8">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
         <v>1.05</v>
@@ -1542,34 +1542,34 @@
         <v>9.5</v>
       </c>
       <c r="Z8">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AA8">
-        <v>3.98</v>
+        <v>3.04</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC8">
+        <v>1.92</v>
+      </c>
+      <c r="AD8">
+        <v>3.59</v>
+      </c>
+      <c r="AE8">
+        <v>1.22</v>
+      </c>
+      <c r="AF8">
+        <v>1.91</v>
+      </c>
+      <c r="AG8">
         <v>1.95</v>
       </c>
-      <c r="AD8">
-        <v>2.89</v>
-      </c>
-      <c r="AE8">
-        <v>1.37</v>
-      </c>
-      <c r="AF8">
-        <v>1.62</v>
-      </c>
-      <c r="AG8">
-        <v>2.1</v>
-      </c>
       <c r="AH8">
-        <v>5.1</v>
+        <v>6.85</v>
       </c>
       <c r="AI8">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AJ8" t="s">
         <v>90</v>
@@ -1637,31 +1637,31 @@
         <v>1.33</v>
       </c>
       <c r="S9">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V9">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AA9">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="AB9">
         <v>1.81</v>
@@ -1670,10 +1670,10 @@
         <v>1.89</v>
       </c>
       <c r="AD9">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AE9">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF9">
         <v>1.75</v>
@@ -1682,10 +1682,10 @@
         <v>1.91</v>
       </c>
       <c r="AH9">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AI9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AJ9" t="s">
         <v>90</v>
@@ -1705,7 +1705,7 @@
         <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1732,76 +1732,76 @@
         <v>89</v>
       </c>
       <c r="L10">
+        <v>1.89</v>
+      </c>
+      <c r="M10">
+        <v>3.5</v>
+      </c>
+      <c r="N10">
+        <v>3.27</v>
+      </c>
+      <c r="O10">
+        <v>1.73</v>
+      </c>
+      <c r="P10">
+        <v>9.5</v>
+      </c>
+      <c r="Q10">
+        <v>2.38</v>
+      </c>
+      <c r="R10">
+        <v>1.3</v>
+      </c>
+      <c r="S10">
+        <v>3.2</v>
+      </c>
+      <c r="T10">
+        <v>2.45</v>
+      </c>
+      <c r="U10">
+        <v>1.5</v>
+      </c>
+      <c r="V10">
+        <v>5.5</v>
+      </c>
+      <c r="W10">
+        <v>1.11</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>9.5</v>
+      </c>
+      <c r="Z10">
+        <v>1.23</v>
+      </c>
+      <c r="AA10">
+        <v>3.98</v>
+      </c>
+      <c r="AB10">
+        <v>1.7</v>
+      </c>
+      <c r="AC10">
+        <v>1.95</v>
+      </c>
+      <c r="AD10">
+        <v>2.6</v>
+      </c>
+      <c r="AE10">
+        <v>1.37</v>
+      </c>
+      <c r="AF10">
         <v>1.67</v>
       </c>
-      <c r="M10">
-        <v>3.58</v>
-      </c>
-      <c r="N10">
-        <v>4.1</v>
-      </c>
-      <c r="O10">
-        <v>1.6</v>
-      </c>
-      <c r="P10">
-        <v>8.5</v>
-      </c>
-      <c r="Q10">
-        <v>2.8</v>
-      </c>
-      <c r="R10">
-        <v>1.39</v>
-      </c>
-      <c r="S10">
-        <v>2.76</v>
-      </c>
-      <c r="T10">
-        <v>2.88</v>
-      </c>
-      <c r="U10">
-        <v>1.36</v>
-      </c>
-      <c r="V10">
-        <v>7</v>
-      </c>
-      <c r="W10">
-        <v>1.09</v>
-      </c>
-      <c r="X10">
-        <v>1.05</v>
-      </c>
-      <c r="Y10">
-        <v>9</v>
-      </c>
-      <c r="Z10">
-        <v>1.3</v>
-      </c>
-      <c r="AA10">
-        <v>3.35</v>
-      </c>
-      <c r="AB10">
-        <v>1.78</v>
-      </c>
-      <c r="AC10">
-        <v>1.92</v>
-      </c>
-      <c r="AD10">
-        <v>3.45</v>
-      </c>
-      <c r="AE10">
-        <v>1.33</v>
-      </c>
-      <c r="AF10">
-        <v>1.85</v>
-      </c>
       <c r="AG10">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH10">
-        <v>6.2</v>
+        <v>5.25</v>
       </c>
       <c r="AI10">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AJ10" t="s">
         <v>90</v>
@@ -1848,13 +1848,13 @@
         <v>89</v>
       </c>
       <c r="L11">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="M11">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N11">
-        <v>3.98</v>
+        <v>3.53</v>
       </c>
       <c r="O11">
         <v>1.67</v>
@@ -1866,55 +1866,55 @@
         <v>2.75</v>
       </c>
       <c r="R11">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="S11">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="T11">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="U11">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V11">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="W11">
         <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Y11">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Z11">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AA11">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AB11">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AC11">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AD11">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG11">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH11">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI11">
         <v>1.01</v>
@@ -1937,7 +1937,7 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
         <v>56</v>
@@ -1964,76 +1964,76 @@
         <v>89</v>
       </c>
       <c r="L12">
-        <v>2.94</v>
+        <v>2.05</v>
       </c>
       <c r="M12">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="N12">
-        <v>1.92</v>
+        <v>4</v>
       </c>
       <c r="O12">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q12">
+        <v>3</v>
+      </c>
+      <c r="R12">
         <v>1.67</v>
       </c>
-      <c r="R12">
-        <v>1.25</v>
-      </c>
       <c r="S12">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="T12">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="U12">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="V12">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="W12">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Z12">
-        <v>1.12</v>
+        <v>1.7</v>
       </c>
       <c r="AA12">
-        <v>5.25</v>
+        <v>2.06</v>
       </c>
       <c r="AB12">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC12">
-        <v>2.49</v>
+        <v>1.33</v>
       </c>
       <c r="AD12">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="AE12">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.4</v>
+        <v>2.63</v>
       </c>
       <c r="AG12">
-        <v>2.64</v>
+        <v>1.44</v>
       </c>
       <c r="AH12">
-        <v>3.5</v>
+        <v>11</v>
       </c>
       <c r="AI12">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="s">
         <v>90</v>
@@ -2053,7 +2053,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
         <v>56</v>
@@ -2080,40 +2080,40 @@
         <v>89</v>
       </c>
       <c r="L13">
-        <v>2.05</v>
+        <v>3.12</v>
       </c>
       <c r="M13">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>2.03</v>
       </c>
       <c r="O13">
+        <v>2.2</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
         <v>1.67</v>
       </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
       <c r="R13">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="S13">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="T13">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
-        <v>1.18</v>
+        <v>1.6</v>
       </c>
       <c r="V13">
-        <v>15</v>
+        <v>4.75</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
         <v>0</v>
@@ -2122,34 +2122,34 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>1.7</v>
+        <v>1.13</v>
       </c>
       <c r="AA13">
-        <v>2.06</v>
+        <v>4.6</v>
       </c>
       <c r="AB13">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC13">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF13">
-        <v>2.63</v>
+        <v>1.48</v>
       </c>
       <c r="AG13">
-        <v>1.44</v>
+        <v>2.57</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ13" t="s">
         <v>90</v>
@@ -2214,34 +2214,34 @@
         <v>2.85</v>
       </c>
       <c r="R14">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="S14">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="T14">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="U14">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="W14">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AA14">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AB14">
         <v>2.05</v>
@@ -2250,22 +2250,22 @@
         <v>1.75</v>
       </c>
       <c r="AD14">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AE14">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AF14">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AH14">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="AI14">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AJ14" t="s">
         <v>90</v>
@@ -2312,13 +2312,13 @@
         <v>89</v>
       </c>
       <c r="L15">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="M15">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="N15">
-        <v>2.27</v>
+        <v>2.56</v>
       </c>
       <c r="O15">
         <v>2.1</v>
@@ -2333,13 +2333,13 @@
         <v>1.3</v>
       </c>
       <c r="S15">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T15">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U15">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V15">
         <v>5.5</v>
@@ -2348,28 +2348,28 @@
         <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA15">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC15">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD15">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AE15">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF15">
         <v>1.57</v>
@@ -2378,10 +2378,10 @@
         <v>2.25</v>
       </c>
       <c r="AH15">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AI15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AJ15" t="s">
         <v>90</v>
@@ -2446,28 +2446,28 @@
         <v>2.45</v>
       </c>
       <c r="R16">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="S16">
         <v>2</v>
       </c>
       <c r="T16">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="U16">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Y16">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Z16">
         <v>1.57</v>
@@ -2485,16 +2485,16 @@
         <v>6.5</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AG16">
         <v>1.5</v>
       </c>
       <c r="AH16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI16">
         <v>1.02</v>
@@ -2562,34 +2562,34 @@
         <v>2.16</v>
       </c>
       <c r="R17">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S17">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="T17">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="U17">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V17">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Z17">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AA17">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AB17">
         <v>2.15</v>
@@ -2598,22 +2598,22 @@
         <v>1.67</v>
       </c>
       <c r="AD17">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AE17">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF17">
+        <v>1.77</v>
+      </c>
+      <c r="AG17">
         <v>1.87</v>
       </c>
-      <c r="AG17">
-        <v>1.8</v>
-      </c>
       <c r="AH17">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="AI17">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AJ17" t="s">
         <v>90</v>

--- a/jogos_2025-07-11.xlsx
+++ b/jogos_2025-07-11.xlsx
@@ -196,24 +196,24 @@
     <t>Aldosivi</t>
   </si>
   <si>
+    <t>Wexford</t>
+  </si>
+  <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Wexford</t>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Waterford</t>
   </si>
   <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>UCD</t>
-  </si>
-  <si>
     <t>Bohemians</t>
   </si>
   <si>
-    <t>Waterford</t>
-  </si>
-  <si>
     <t>Vila Nova</t>
   </si>
   <si>
@@ -229,12 +229,12 @@
     <t>Austin II</t>
   </si>
   <si>
+    <t>Monterey Bay</t>
+  </si>
+  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
-    <t>Monterey Bay</t>
-  </si>
-  <si>
     <t>Blacktown City</t>
   </si>
   <si>
@@ -244,24 +244,24 @@
     <t>Central Córdoba SdE</t>
   </si>
   <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
     <t>Cobh Ramblers</t>
   </si>
   <si>
-    <t>Athlone Town</t>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Cork City</t>
   </si>
   <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
@@ -277,10 +277,10 @@
     <t>St. Louis City II</t>
   </si>
   <si>
+    <t>Orange County SC</t>
+  </si>
+  <si>
     <t>Patronato</t>
-  </si>
-  <si>
-    <t>Orange County SC</t>
   </si>
   <si>
     <t>incomplete</t>
@@ -804,13 +804,13 @@
         <v>89</v>
       </c>
       <c r="L2">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="M2">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="N2">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="O2">
         <v>2.1</v>
@@ -822,25 +822,25 @@
         <v>1.73</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T2">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V2">
         <v>5.5</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
         <v>10</v>
@@ -852,28 +852,28 @@
         <v>3.9</v>
       </c>
       <c r="AB2">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD2">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AE2">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG2">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH2">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AI2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AJ2" t="s">
         <v>90</v>
@@ -938,13 +938,13 @@
         <v>2.08</v>
       </c>
       <c r="R3">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S3">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="U3">
         <v>1.57</v>
@@ -953,10 +953,10 @@
         <v>5</v>
       </c>
       <c r="W3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
         <v>15</v>
@@ -965,7 +965,7 @@
         <v>1.18</v>
       </c>
       <c r="AA3">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB3">
         <v>1.51</v>
@@ -980,10 +980,10 @@
         <v>1.53</v>
       </c>
       <c r="AF3">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AG3">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH3">
         <v>3.9</v>
@@ -1152,76 +1152,76 @@
         <v>89</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="M5">
-        <v>3.38</v>
+        <v>3.68</v>
       </c>
       <c r="N5">
-        <v>2.04</v>
+        <v>3.47</v>
       </c>
       <c r="O5">
+        <v>1.73</v>
+      </c>
+      <c r="P5">
+        <v>10</v>
+      </c>
+      <c r="Q5">
         <v>2.3</v>
       </c>
-      <c r="P5">
-        <v>9.5</v>
-      </c>
-      <c r="Q5">
-        <v>1.8</v>
-      </c>
       <c r="R5">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T5">
-        <v>2.72</v>
+        <v>2.34</v>
       </c>
       <c r="U5">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="V5">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Z5">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AA5">
-        <v>3.48</v>
+        <v>4.75</v>
       </c>
       <c r="AB5">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="AC5">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AD5">
-        <v>3.15</v>
+        <v>2.08</v>
       </c>
       <c r="AE5">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG5">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH5">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="AI5">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AJ5" t="s">
         <v>90</v>
@@ -1268,76 +1268,76 @@
         <v>89</v>
       </c>
       <c r="L6">
-        <v>1.79</v>
+        <v>3</v>
       </c>
       <c r="M6">
-        <v>3.68</v>
+        <v>3.38</v>
       </c>
       <c r="N6">
-        <v>3.47</v>
+        <v>2.04</v>
       </c>
       <c r="O6">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q6">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="R6">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S6">
+        <v>2.9</v>
+      </c>
+      <c r="T6">
+        <v>2.6</v>
+      </c>
+      <c r="U6">
+        <v>1.42</v>
+      </c>
+      <c r="V6">
+        <v>6.5</v>
+      </c>
+      <c r="W6">
+        <v>1.09</v>
+      </c>
+      <c r="X6">
+        <v>1.04</v>
+      </c>
+      <c r="Y6">
+        <v>9</v>
+      </c>
+      <c r="Z6">
+        <v>1.27</v>
+      </c>
+      <c r="AA6">
         <v>3.4</v>
       </c>
-      <c r="T6">
-        <v>2.3</v>
-      </c>
-      <c r="U6">
-        <v>1.57</v>
-      </c>
-      <c r="V6">
-        <v>4.5</v>
-      </c>
-      <c r="W6">
-        <v>1.15</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6">
-        <v>13.5</v>
-      </c>
-      <c r="Z6">
-        <v>1.16</v>
-      </c>
-      <c r="AA6">
-        <v>4.75</v>
-      </c>
       <c r="AB6">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="AC6">
-        <v>2.33</v>
+        <v>1.9</v>
       </c>
       <c r="AD6">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="AE6">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AF6">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG6">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="AH6">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AI6">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="s">
         <v>90</v>
@@ -1384,73 +1384,73 @@
         <v>89</v>
       </c>
       <c r="L7">
-        <v>3.63</v>
+        <v>1.67</v>
       </c>
       <c r="M7">
-        <v>3.45</v>
+        <v>3.58</v>
       </c>
       <c r="N7">
+        <v>4.1</v>
+      </c>
+      <c r="O7">
+        <v>1.6</v>
+      </c>
+      <c r="P7">
+        <v>8.5</v>
+      </c>
+      <c r="Q7">
+        <v>2.8</v>
+      </c>
+      <c r="R7">
+        <v>1.4</v>
+      </c>
+      <c r="S7">
+        <v>2.7</v>
+      </c>
+      <c r="T7">
+        <v>2.8</v>
+      </c>
+      <c r="U7">
+        <v>1.37</v>
+      </c>
+      <c r="V7">
+        <v>7.25</v>
+      </c>
+      <c r="W7">
+        <v>1.08</v>
+      </c>
+      <c r="X7">
+        <v>1.06</v>
+      </c>
+      <c r="Y7">
+        <v>8.25</v>
+      </c>
+      <c r="Z7">
+        <v>1.33</v>
+      </c>
+      <c r="AA7">
+        <v>3</v>
+      </c>
+      <c r="AB7">
+        <v>1.78</v>
+      </c>
+      <c r="AC7">
+        <v>1.92</v>
+      </c>
+      <c r="AD7">
+        <v>3.4</v>
+      </c>
+      <c r="AE7">
+        <v>1.27</v>
+      </c>
+      <c r="AF7">
         <v>1.81</v>
       </c>
-      <c r="O7">
-        <v>2.5</v>
-      </c>
-      <c r="P7">
-        <v>9</v>
-      </c>
-      <c r="Q7">
-        <v>1.67</v>
-      </c>
-      <c r="R7">
-        <v>1.3</v>
-      </c>
-      <c r="S7">
-        <v>3.1</v>
-      </c>
-      <c r="T7">
-        <v>2.6</v>
-      </c>
-      <c r="U7">
-        <v>1.4</v>
-      </c>
-      <c r="V7">
-        <v>5.5</v>
-      </c>
-      <c r="W7">
-        <v>1.1</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>10</v>
-      </c>
-      <c r="Z7">
-        <v>1.3</v>
-      </c>
-      <c r="AA7">
-        <v>3.92</v>
-      </c>
-      <c r="AB7">
-        <v>1.79</v>
-      </c>
-      <c r="AC7">
-        <v>1.91</v>
-      </c>
-      <c r="AD7">
-        <v>2.7</v>
-      </c>
-      <c r="AE7">
-        <v>1.3</v>
-      </c>
-      <c r="AF7">
+      <c r="AG7">
         <v>1.75</v>
       </c>
-      <c r="AG7">
-        <v>2</v>
-      </c>
       <c r="AH7">
-        <v>5.4</v>
+        <v>6.75</v>
       </c>
       <c r="AI7">
         <v>1.09</v>
@@ -1473,7 +1473,7 @@
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1500,76 +1500,76 @@
         <v>89</v>
       </c>
       <c r="L8">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="M8">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>3.27</v>
       </c>
       <c r="O8">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="P8">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q8">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="R8">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="S8">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="T8">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="U8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z8">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AA8">
-        <v>3.04</v>
+        <v>3.95</v>
       </c>
       <c r="AB8">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AD8">
-        <v>3.59</v>
+        <v>2.75</v>
       </c>
       <c r="AE8">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AF8">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AG8">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH8">
-        <v>6.85</v>
+        <v>5</v>
       </c>
       <c r="AI8">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AJ8" t="s">
         <v>90</v>
@@ -1589,7 +1589,7 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1616,76 +1616,76 @@
         <v>89</v>
       </c>
       <c r="L9">
-        <v>1.6</v>
+        <v>3.63</v>
       </c>
       <c r="M9">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N9">
-        <v>4.6</v>
+        <v>1.81</v>
       </c>
       <c r="O9">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="P9">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="R9">
         <v>1.33</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U9">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="Z9">
         <v>1.25</v>
       </c>
       <c r="AA9">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB9">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AC9">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AD9">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AE9">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AF9">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AH9">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="AI9">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AJ9" t="s">
         <v>90</v>
@@ -1732,73 +1732,73 @@
         <v>89</v>
       </c>
       <c r="L10">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="M10">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N10">
-        <v>3.27</v>
+        <v>4.6</v>
       </c>
       <c r="O10">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="P10">
         <v>9.5</v>
       </c>
       <c r="Q10">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="R10">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S10">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T10">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="U10">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V10">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="Z10">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AA10">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="AB10">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AC10">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AD10">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AE10">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AH10">
-        <v>5.25</v>
+        <v>6.05</v>
       </c>
       <c r="AI10">
         <v>1.13</v>
@@ -1848,13 +1848,13 @@
         <v>89</v>
       </c>
       <c r="L11">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="M11">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N11">
-        <v>3.53</v>
+        <v>3.98</v>
       </c>
       <c r="O11">
         <v>1.67</v>
@@ -1875,31 +1875,31 @@
         <v>3.75</v>
       </c>
       <c r="U11">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V11">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y11">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Z11">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AA11">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AB11">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AC11">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AD11">
         <v>5.25</v>
@@ -1911,10 +1911,10 @@
         <v>2.15</v>
       </c>
       <c r="AG11">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AH11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI11">
         <v>1.01</v>
@@ -2080,10 +2080,10 @@
         <v>89</v>
       </c>
       <c r="L13">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="M13">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="N13">
         <v>2.03</v>
@@ -2107,7 +2107,7 @@
         <v>2.2</v>
       </c>
       <c r="U13">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="V13">
         <v>4.75</v>
@@ -2122,31 +2122,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AA13">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AB13">
         <v>1.5</v>
       </c>
       <c r="AC13">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD13">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AE13">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF13">
         <v>1.48</v>
       </c>
       <c r="AG13">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AH13">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AI13">
         <v>1.22</v>
@@ -2196,13 +2196,13 @@
         <v>89</v>
       </c>
       <c r="L14">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="M14">
+        <v>3.6</v>
+      </c>
+      <c r="N14">
         <v>3.5</v>
-      </c>
-      <c r="N14">
-        <v>4.4</v>
       </c>
       <c r="O14">
         <v>1.54</v>
@@ -2214,46 +2214,46 @@
         <v>2.85</v>
       </c>
       <c r="R14">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S14">
         <v>2.95</v>
       </c>
       <c r="T14">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
         <v>1.42</v>
       </c>
       <c r="V14">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
         <v>10</v>
       </c>
       <c r="Z14">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AA14">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AC14">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AD14">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AE14">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF14">
         <v>1.7</v>
@@ -2262,10 +2262,10 @@
         <v>2.05</v>
       </c>
       <c r="AH14">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AI14">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AJ14" t="s">
         <v>90</v>
@@ -2312,13 +2312,13 @@
         <v>89</v>
       </c>
       <c r="L15">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="M15">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N15">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O15">
         <v>2.1</v>
@@ -2336,16 +2336,16 @@
         <v>3</v>
       </c>
       <c r="T15">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="U15">
         <v>1.45</v>
       </c>
       <c r="V15">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
         <v>1.02</v>
@@ -2354,34 +2354,34 @@
         <v>10</v>
       </c>
       <c r="Z15">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AA15">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AB15">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC15">
         <v>2</v>
       </c>
       <c r="AD15">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AE15">
         <v>1.4</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH15">
         <v>4.5</v>
       </c>
       <c r="AI15">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ15" t="s">
         <v>90</v>
@@ -2401,7 +2401,7 @@
         <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
         <v>56</v>
@@ -2428,76 +2428,76 @@
         <v>89</v>
       </c>
       <c r="L16">
-        <v>2.14</v>
+        <v>2.69</v>
       </c>
       <c r="M16">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="N16">
-        <v>3.27</v>
+        <v>2.38</v>
       </c>
       <c r="O16">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="P16">
-        <v>5.75</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q16">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="R16">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="S16">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="T16">
-        <v>4.3</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="V16">
-        <v>12</v>
+        <v>7.7</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>4.7</v>
+        <v>8.5</v>
       </c>
       <c r="Z16">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AA16">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AB16">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="AC16">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AD16">
+        <v>3.7</v>
+      </c>
+      <c r="AE16">
+        <v>1.29</v>
+      </c>
+      <c r="AF16">
+        <v>1.8</v>
+      </c>
+      <c r="AG16">
+        <v>1.95</v>
+      </c>
+      <c r="AH16">
         <v>6.5</v>
       </c>
-      <c r="AE16">
-        <v>1.07</v>
-      </c>
-      <c r="AF16">
-        <v>2.55</v>
-      </c>
-      <c r="AG16">
-        <v>1.5</v>
-      </c>
-      <c r="AH16">
-        <v>15</v>
-      </c>
       <c r="AI16">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AJ16" t="s">
         <v>90</v>
@@ -2517,7 +2517,7 @@
         <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
         <v>56</v>
@@ -2544,76 +2544,76 @@
         <v>89</v>
       </c>
       <c r="L17">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="M17">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="N17">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="O17">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="P17">
-        <v>8.699999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="Q17">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="R17">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="S17">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="T17">
-        <v>2.93</v>
+        <v>4.33</v>
       </c>
       <c r="U17">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="V17">
-        <v>7.7</v>
+        <v>12</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="Y17">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="Z17">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AA17">
-        <v>3.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>2.15</v>
+        <v>3.21</v>
       </c>
       <c r="AC17">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AD17">
-        <v>3.58</v>
+        <v>6.5</v>
       </c>
       <c r="AE17">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.77</v>
+        <v>2.6</v>
       </c>
       <c r="AG17">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AH17">
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="AI17">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AJ17" t="s">
         <v>90</v>

--- a/jogos_2025-07-11.xlsx
+++ b/jogos_2025-07-11.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -196,24 +196,24 @@
     <t>Aldosivi</t>
   </si>
   <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Waterford</t>
+  </si>
+  <si>
     <t>Wexford</t>
   </si>
   <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
     <t>Vila Nova</t>
   </si>
   <si>
@@ -244,24 +244,24 @@
     <t>Central Córdoba SdE</t>
   </si>
   <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
     <t>Athlone Town</t>
   </si>
   <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
     <t>Operário PR</t>
   </si>
   <si>
@@ -283,10 +283,76 @@
     <t>Patronato</t>
   </si>
   <si>
-    <t>incomplete</t>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>['29', '33', '87']</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['43', '90+3']</t>
+  </si>
+  <si>
+    <t>['50', '87']</t>
+  </si>
+  <si>
+    <t>['16', '45+3', '50']</t>
+  </si>
+  <si>
+    <t>['47', '72', '61']</t>
+  </si>
+  <si>
+    <t>['36', '21']</t>
+  </si>
+  <si>
+    <t>['45+2']</t>
+  </si>
+  <si>
+    <t>['18', '38']</t>
+  </si>
+  <si>
+    <t>['40', '90+9']</t>
+  </si>
+  <si>
+    <t>['78', '90+4']</t>
+  </si>
+  <si>
+    <t>['39', '54']</t>
+  </si>
+  <si>
+    <t>['25', '90+2']</t>
+  </si>
+  <si>
+    <t>['64', '82']</t>
+  </si>
+  <si>
+    <t>['4', '49']</t>
+  </si>
+  <si>
+    <t>['57']</t>
+  </si>
+  <si>
+    <t>['21']</t>
+  </si>
+  <si>
+    <t>['3', '85']</t>
+  </si>
+  <si>
+    <t>['73', '90+6']</t>
+  </si>
+  <si>
+    <t>['63', '45', '56']</t>
+  </si>
+  <si>
+    <t>['17', '12', '24', '39']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['48']</t>
   </si>
 </sst>
 </file>
@@ -789,13 +855,13 @@
         <v>73</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -804,13 +870,13 @@
         <v>89</v>
       </c>
       <c r="L2">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="M2">
-        <v>3.72</v>
+        <v>3.6</v>
       </c>
       <c r="N2">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="O2">
         <v>2.1</v>
@@ -825,61 +891,61 @@
         <v>1.33</v>
       </c>
       <c r="S2">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T2">
         <v>2.5</v>
       </c>
       <c r="U2">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V2">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
         <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AB2">
         <v>1.7</v>
       </c>
       <c r="AC2">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AD2">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AE2">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF2">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AG2">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AH2">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="AI2">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AJ2" t="s">
         <v>90</v>
       </c>
       <c r="AK2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="AL2" s="3">
         <v>45849.27083333334</v>
@@ -908,25 +974,25 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
         <v>89</v>
       </c>
       <c r="L3">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="M3">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N3">
-        <v>2.91</v>
+        <v>2.82</v>
       </c>
       <c r="O3">
         <v>1.73</v>
@@ -938,22 +1004,22 @@
         <v>2.08</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T3">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="W3">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X3">
         <v>1.03</v>
@@ -962,40 +1028,40 @@
         <v>15</v>
       </c>
       <c r="Z3">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AA3">
         <v>4.5</v>
       </c>
       <c r="AB3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC3">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="AD3">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AE3">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG3">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH3">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AI3">
         <v>1.22</v>
       </c>
       <c r="AJ3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AK3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="AL3" s="3">
         <v>45849.54166666666</v>
@@ -1108,10 +1174,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AK4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AL4" s="3">
         <v>45849.64583333334</v>
@@ -1137,13 +1203,13 @@
         <v>76</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1152,82 +1218,82 @@
         <v>89</v>
       </c>
       <c r="L5">
-        <v>1.79</v>
+        <v>4.1</v>
       </c>
       <c r="M5">
         <v>3.68</v>
       </c>
       <c r="N5">
-        <v>3.47</v>
+        <v>1.7</v>
       </c>
       <c r="O5">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="P5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T5">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="U5">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V5">
         <v>5</v>
       </c>
       <c r="W5">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA5">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AB5">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AC5">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AD5">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="AE5">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH5">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="AI5">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AJ5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AK5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AL5" s="3">
         <v>45849.65625</v>
@@ -1253,10 +1319,10 @@
         <v>77</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1268,13 +1334,13 @@
         <v>89</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="M6">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N6">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="O6">
         <v>2.3</v>
@@ -1286,64 +1352,64 @@
         <v>1.8</v>
       </c>
       <c r="R6">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>2.9</v>
+        <v>3.24</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="U6">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V6">
         <v>6.5</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>9</v>
       </c>
       <c r="Z6">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AA6">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AB6">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC6">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD6">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AE6">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AF6">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AG6">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH6">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="AI6">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AK6" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AL6" s="3">
         <v>45849.65625</v>
@@ -1369,28 +1435,28 @@
         <v>78</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="s">
         <v>89</v>
       </c>
       <c r="L7">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="M7">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="N7">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O7">
         <v>1.6</v>
@@ -1402,64 +1468,64 @@
         <v>2.8</v>
       </c>
       <c r="R7">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S7">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="U7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V7">
-        <v>7.25</v>
+        <v>6.9</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>8.25</v>
+        <v>9.5</v>
       </c>
       <c r="Z7">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AA7">
-        <v>3</v>
+        <v>3.39</v>
       </c>
       <c r="AB7">
+        <v>2</v>
+      </c>
+      <c r="AC7">
         <v>1.78</v>
       </c>
-      <c r="AC7">
-        <v>1.92</v>
-      </c>
       <c r="AD7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AE7">
         <v>1.27</v>
       </c>
       <c r="AF7">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG7">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH7">
-        <v>6.75</v>
+        <v>6.64</v>
       </c>
       <c r="AI7">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AK7" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AL7" s="3">
         <v>45849.65625</v>
@@ -1485,7 +1551,7 @@
         <v>79</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1500,82 +1566,82 @@
         <v>89</v>
       </c>
       <c r="L8">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="M8">
-        <v>3.5</v>
+        <v>4.04</v>
       </c>
       <c r="N8">
-        <v>3.27</v>
+        <v>5.4</v>
       </c>
       <c r="O8">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="P8">
         <v>9.5</v>
       </c>
       <c r="Q8">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S8">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="T8">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="U8">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V8">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y8">
         <v>10.5</v>
       </c>
       <c r="Z8">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AA8">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC8">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AD8">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AE8">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AF8">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AG8">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH8">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="AI8">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AJ8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AL8" s="3">
         <v>45849.65625</v>
@@ -1589,7 +1655,7 @@
         <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1601,13 +1667,13 @@
         <v>80</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1616,82 +1682,82 @@
         <v>89</v>
       </c>
       <c r="L9">
-        <v>3.63</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N9">
-        <v>1.81</v>
+        <v>3.35</v>
       </c>
       <c r="O9">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="P9">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Q9">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="R9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="T9">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U9">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V9">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y9">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AA9">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AB9">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC9">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AD9">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AE9">
         <v>1.3</v>
       </c>
       <c r="AF9">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG9">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH9">
-        <v>5.25</v>
+        <v>6.35</v>
       </c>
       <c r="AI9">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AJ9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AK9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AL9" s="3">
         <v>45849.65625</v>
@@ -1705,7 +1771,7 @@
         <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
         <v>56</v>
@@ -1732,82 +1798,82 @@
         <v>89</v>
       </c>
       <c r="L10">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="M10">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N10">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="O10">
+        <v>1.73</v>
+      </c>
+      <c r="P10">
+        <v>10</v>
+      </c>
+      <c r="Q10">
+        <v>2.3</v>
+      </c>
+      <c r="R10">
+        <v>1.3</v>
+      </c>
+      <c r="S10">
+        <v>3.2</v>
+      </c>
+      <c r="T10">
+        <v>2.35</v>
+      </c>
+      <c r="U10">
+        <v>1.55</v>
+      </c>
+      <c r="V10">
+        <v>5.5</v>
+      </c>
+      <c r="W10">
+        <v>1.12</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>12</v>
+      </c>
+      <c r="Z10">
+        <v>1.2</v>
+      </c>
+      <c r="AA10">
+        <v>4.33</v>
+      </c>
+      <c r="AB10">
+        <v>1.61</v>
+      </c>
+      <c r="AC10">
+        <v>2.25</v>
+      </c>
+      <c r="AD10">
+        <v>2.49</v>
+      </c>
+      <c r="AE10">
+        <v>1.5</v>
+      </c>
+      <c r="AF10">
         <v>1.53</v>
       </c>
-      <c r="P10">
-        <v>9.5</v>
-      </c>
-      <c r="Q10">
-        <v>2.9</v>
-      </c>
-      <c r="R10">
-        <v>1.36</v>
-      </c>
-      <c r="S10">
-        <v>2.9</v>
-      </c>
-      <c r="T10">
-        <v>2.6</v>
-      </c>
-      <c r="U10">
-        <v>1.43</v>
-      </c>
-      <c r="V10">
-        <v>6.5</v>
-      </c>
-      <c r="W10">
-        <v>1.09</v>
-      </c>
-      <c r="X10">
-        <v>1.04</v>
-      </c>
-      <c r="Y10">
-        <v>9.75</v>
-      </c>
-      <c r="Z10">
-        <v>1.26</v>
-      </c>
-      <c r="AA10">
-        <v>3.4</v>
-      </c>
-      <c r="AB10">
-        <v>1.81</v>
-      </c>
-      <c r="AC10">
-        <v>1.89</v>
-      </c>
-      <c r="AD10">
-        <v>3</v>
-      </c>
-      <c r="AE10">
-        <v>1.34</v>
-      </c>
-      <c r="AF10">
-        <v>1.82</v>
-      </c>
       <c r="AG10">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH10">
-        <v>6.05</v>
+        <v>4.5</v>
       </c>
       <c r="AI10">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AJ10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AK10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AL10" s="3">
         <v>45849.65625</v>
@@ -1848,13 +1914,13 @@
         <v>89</v>
       </c>
       <c r="L11">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="M11">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="N11">
-        <v>3.98</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
         <v>1.67</v>
@@ -1866,64 +1932,64 @@
         <v>2.75</v>
       </c>
       <c r="R11">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S11">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T11">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="U11">
         <v>1.22</v>
       </c>
       <c r="V11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y11">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="Z11">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA11">
+        <v>2.15</v>
+      </c>
+      <c r="AB11">
+        <v>2.88</v>
+      </c>
+      <c r="AC11">
+        <v>1.42</v>
+      </c>
+      <c r="AD11">
+        <v>6.19</v>
+      </c>
+      <c r="AE11">
+        <v>1.11</v>
+      </c>
+      <c r="AF11">
         <v>2.3</v>
       </c>
-      <c r="AB11">
-        <v>2.45</v>
-      </c>
-      <c r="AC11">
-        <v>1.48</v>
-      </c>
-      <c r="AD11">
-        <v>5.25</v>
-      </c>
-      <c r="AE11">
-        <v>1.12</v>
-      </c>
-      <c r="AF11">
-        <v>2.15</v>
-      </c>
       <c r="AG11">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AH11">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AI11">
         <v>1.01</v>
       </c>
       <c r="AJ11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AK11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AL11" s="3">
         <v>45849.79166666666</v>
@@ -1949,16 +2015,16 @@
         <v>83</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="s">
         <v>89</v>
@@ -2036,10 +2102,10 @@
         <v>1.03</v>
       </c>
       <c r="AJ12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="AK12" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="AL12" s="3">
         <v>45849.83333333334</v>
@@ -2065,13 +2131,13 @@
         <v>84</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2080,13 +2146,13 @@
         <v>89</v>
       </c>
       <c r="L13">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="M13">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="N13">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O13">
         <v>2.2</v>
@@ -2098,7 +2164,7 @@
         <v>1.67</v>
       </c>
       <c r="R13">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S13">
         <v>3.6</v>
@@ -2107,55 +2173,55 @@
         <v>2.2</v>
       </c>
       <c r="U13">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="V13">
         <v>4.75</v>
       </c>
       <c r="W13">
+        <v>1.17</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
+        <v>12</v>
+      </c>
+      <c r="Z13">
         <v>1.15</v>
       </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>1.14</v>
-      </c>
       <c r="AA13">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AB13">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AC13">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD13">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AE13">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AF13">
         <v>1.48</v>
       </c>
       <c r="AG13">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="AH13">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AI13">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AJ13" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="AL13" s="3">
         <v>45849.83333333334</v>
@@ -2181,16 +2247,16 @@
         <v>85</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="s">
         <v>89</v>
@@ -2214,34 +2280,34 @@
         <v>2.85</v>
       </c>
       <c r="R14">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S14">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="T14">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U14">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V14">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z14">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AA14">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="AB14">
         <v>1.76</v>
@@ -2250,28 +2316,28 @@
         <v>1.94</v>
       </c>
       <c r="AD14">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="AE14">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AG14">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH14">
-        <v>5.5</v>
+        <v>6.65</v>
       </c>
       <c r="AI14">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="AL14" s="3">
         <v>45849.85416666666</v>
@@ -2297,28 +2363,28 @@
         <v>86</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K15" t="s">
         <v>89</v>
       </c>
       <c r="L15">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="M15">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="N15">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="O15">
         <v>2.1</v>
@@ -2330,64 +2396,64 @@
         <v>1.8</v>
       </c>
       <c r="R15">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S15">
         <v>3</v>
       </c>
       <c r="T15">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V15">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z15">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AA15">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="AB15">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC15">
         <v>2</v>
       </c>
       <c r="AD15">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AE15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AH15">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AI15">
         <v>1.13</v>
       </c>
       <c r="AJ15" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AK15" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AL15" s="3">
         <v>45849.89583333334</v>
@@ -2413,13 +2479,13 @@
         <v>87</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2449,10 +2515,10 @@
         <v>1.4</v>
       </c>
       <c r="S16">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="U16">
         <v>1.36</v>
@@ -2473,7 +2539,7 @@
         <v>1.33</v>
       </c>
       <c r="AA16">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB16">
         <v>1.95</v>
@@ -2482,28 +2548,28 @@
         <v>1.7</v>
       </c>
       <c r="AD16">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AE16">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH16">
         <v>6.5</v>
       </c>
       <c r="AI16">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AJ16" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="AL16" s="3">
         <v>45849.91666666666</v>
@@ -2529,13 +2595,13 @@
         <v>88</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2562,28 +2628,28 @@
         <v>2.45</v>
       </c>
       <c r="R17">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S17">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="T17">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="U17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V17">
         <v>12</v>
       </c>
       <c r="W17">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Z17">
         <v>1.57</v>
@@ -2601,13 +2667,13 @@
         <v>6.5</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF17">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="AG17">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH17">
         <v>13</v>
@@ -2616,10 +2682,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ17" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="AK17" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="AL17" s="3">
         <v>45849.91666666666</v>

--- a/jogos_2025-07-11.xlsx
+++ b/jogos_2025-07-11.xlsx
@@ -762,97 +762,97 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -861,20 +861,20 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '90']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45849.54166666666</v>
@@ -891,97 +891,97 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -990,20 +990,20 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['4', '49']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45849.54166666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.77</v>
+        <v>2.03</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="N5" t="n">
-        <v>1.52</v>
+        <v>2.82</v>
       </c>
       <c r="O5" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.38</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AA5" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['4', '49']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.73</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['21', '90']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>1.6</v>
+        <v>2.08</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45849.54166666666</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.55</v>
+        <v>4.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="U8" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>4.33</v>
+        <v>3.39</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.49</v>
+        <v>3.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '45+3', '50']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AG8" t="n">
         <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45849.65625</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.61</v>
       </c>
-      <c r="M10" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.25</v>
       </c>
-      <c r="X10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['47', '72', '61']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH10" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45849.65625</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.67</v>
+        <v>1.61</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>4.04</v>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>3.8</v>
+        <v>2.21</v>
       </c>
       <c r="P11" t="n">
         <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.51</v>
+        <v>4.7</v>
       </c>
       <c r="R11" t="n">
         <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W11" t="n">
         <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="Z11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['50', '87']</t>
+          <t>['47', '72', '61']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.15</v>
+        <v>2.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45849.65625</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.92</v>
+        <v>4.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.56</v>
+        <v>2.35</v>
       </c>
       <c r="R12" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>3.39</v>
+        <v>3.85</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['16', '45+3', '50']</t>
+          <t>['43', '90+3']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45849.65625</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.1</v>
+        <v>3.67</v>
       </c>
       <c r="M13" t="n">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="R13" t="n">
         <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.4</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC13" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['43', '90+3']</t>
+          <t>['50', '87']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45849.65625</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Talleres Córdoba</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.28</v>
+        <v>2.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.69</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="P15" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>4.75</v>
+        <v>2.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.45</v>
+        <v>3.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.57</v>
+        <v>1.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.48</v>
+        <v>2.63</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['18', '38']</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['73', '90+6']</t>
+          <t>['3', '85']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45849.83333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Talleres Córdoba</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.05</v>
+        <v>3.28</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.69</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.5</v>
+        <v>2.38</v>
       </c>
       <c r="R17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['18', '38']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['73', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.67</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['45+2']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['3', '85']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45849.83333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.14</v>
+        <v>2.69</v>
       </c>
       <c r="M21" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.27</v>
+        <v>2.38</v>
       </c>
       <c r="O21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X21" t="n">
         <v>3</v>
       </c>
-      <c r="P21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="Y21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.73</v>
       </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.69</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['25', '90+2']</t>
+          <t>['39', '54']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AG21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.48</v>
       </c>
-      <c r="AH21" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AI21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45849.91666666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC22" t="n">
         <v>2.69</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['39', '54']</t>
+          <t>['25', '90+2']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45849.91666666666</v>
